--- a/artfynd/A 60495-2025 artfynd.xlsx
+++ b/artfynd/A 60495-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -907,45 +907,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135076109</v>
+        <v>135130177</v>
       </c>
       <c r="B4" t="n">
-        <v>93271</v>
+        <v>97308</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>2869</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -953,13 +946,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520057</v>
+        <v>520064</v>
       </c>
       <c r="R4" t="n">
-        <v>6339602</v>
+        <v>6339661</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,34 +979,25 @@
           <t>2026-07-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>16:03</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-07-11</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>16:03</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Invid äldre tall.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Granskog, källflöde/kärrdråg</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1030,36 +1014,44 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135076106</v>
+        <v>135076109</v>
       </c>
       <c r="B5" t="n">
-        <v>91937</v>
+        <v>93271</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1068,13 +1060,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519988</v>
+        <v>520057</v>
       </c>
       <c r="R5" t="n">
-        <v>6339696</v>
+        <v>6339602</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1103,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1113,7 +1105,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Invid äldre tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,7 +1137,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135076107</v>
+        <v>135076106</v>
       </c>
       <c r="B6" t="n">
         <v>91937</v>
@@ -1178,13 +1175,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520000</v>
+        <v>519988</v>
       </c>
       <c r="R6" t="n">
-        <v>6339704</v>
+        <v>6339696</v>
       </c>
       <c r="S6" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1213,7 +1210,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1220,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1247,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135076099</v>
+        <v>135076107</v>
       </c>
       <c r="B7" t="n">
-        <v>4782</v>
+        <v>91937</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,32 +1258,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102306</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1294,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520075</v>
+        <v>520000</v>
       </c>
       <c r="R7" t="n">
-        <v>6339676</v>
+        <v>6339704</v>
       </c>
       <c r="S7" t="n">
         <v>16</v>
@@ -1329,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135076116</v>
+        <v>135076099</v>
       </c>
       <c r="B8" t="n">
-        <v>106324</v>
+        <v>4782</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,35 +1368,32 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>102306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1413,10 +1401,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520000</v>
+        <v>520075</v>
       </c>
       <c r="R8" t="n">
-        <v>6339704</v>
+        <v>6339676</v>
       </c>
       <c r="S8" t="n">
         <v>16</v>
@@ -1448,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1458,7 +1446,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1485,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135076115</v>
+        <v>135076116</v>
       </c>
       <c r="B9" t="n">
-        <v>104878</v>
+        <v>106324</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1496,26 +1484,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221178</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bäckbräsma</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cardamine amara</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1523,11 +1511,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1536,13 +1520,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520064</v>
+        <v>520000</v>
       </c>
       <c r="R9" t="n">
-        <v>6339661</v>
+        <v>6339704</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1571,7 +1555,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>22:24</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1581,12 +1565,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>22:25</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Surdråg, källflöde.</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1610,6 +1589,134 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135076115</v>
+      </c>
+      <c r="B10" t="n">
+        <v>104878</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221178</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bäckbräsma</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Cardamine amara</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Planen, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>520064</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6339661</v>
+      </c>
+      <c r="S10" t="n">
+        <v>8</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Åseda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>22:24</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>22:25</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Surdråg, källflöde.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Raul Vicente</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Raul Vicente</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
